--- a/tabelas/2026.xlsx
+++ b/tabelas/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapiloto-portoflio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1B5C55-1C4E-4DAF-BD0E-4C69DFC190A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5A2B7E7-FE31-4D0C-ABC0-3A51C93C022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="1044">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -153,9 +153,6 @@
     <t>CONCRETO</t>
   </si>
   <si>
-    <t>08.777.142.0012.000</t>
-  </si>
-  <si>
     <t>08.777.142.0012.001</t>
   </si>
   <si>
@@ -3147,13 +3144,19 @@
     <t>08.777.142.0012.997</t>
   </si>
   <si>
-    <t>08.777.142.0012.998</t>
-  </si>
-  <si>
     <t>SEM CONSRRUÇÃO</t>
   </si>
   <si>
     <t>INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>08.777.141.0012.000</t>
+  </si>
+  <si>
+    <t>08.777.143.0012.998</t>
+  </si>
+  <si>
+    <t>08.777.143.0024.999</t>
   </si>
 </sst>
 </file>
@@ -3518,7 +3521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEC8DEA-D1AE-4B91-B66D-48CA0A2026FB}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -3555,7 +3558,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>1041</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
@@ -3573,12 +3576,12 @@
         <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>4</v>
@@ -3601,7 +3604,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -3624,7 +3627,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>4</v>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>4</v>
@@ -3670,7 +3673,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>4</v>
@@ -3693,7 +3696,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>4</v>
@@ -3716,7 +3719,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>4</v>
@@ -3739,7 +3742,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>4</v>
@@ -3762,7 +3765,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>4</v>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>4</v>
@@ -3808,7 +3811,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>4</v>
@@ -3831,7 +3834,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>4</v>
@@ -3854,7 +3857,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>4</v>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>4</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>4</v>
@@ -3923,7 +3926,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>4</v>
@@ -3946,7 +3949,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>4</v>
@@ -3969,7 +3972,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>4</v>
@@ -3992,7 +3995,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>4</v>
@@ -4015,7 +4018,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>4</v>
@@ -4038,7 +4041,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>4</v>
@@ -4061,7 +4064,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>4</v>
@@ -4084,7 +4087,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>4</v>
@@ -4107,7 +4110,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>4</v>
@@ -4130,7 +4133,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>4</v>
@@ -4153,7 +4156,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>4</v>
@@ -4176,7 +4179,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>4</v>
@@ -4199,7 +4202,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>4</v>
@@ -4222,7 +4225,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>4</v>
@@ -4245,7 +4248,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>4</v>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>4</v>
@@ -4291,7 +4294,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>5</v>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
@@ -4337,7 +4340,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>5</v>
@@ -4360,7 +4363,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>5</v>
@@ -4383,7 +4386,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>5</v>
@@ -4406,7 +4409,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>5</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>5</v>
@@ -4452,7 +4455,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>5</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>5</v>
@@ -4498,7 +4501,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>5</v>
@@ -4521,7 +4524,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>5</v>
@@ -4544,7 +4547,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>5</v>
@@ -4567,7 +4570,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>5</v>
@@ -4590,7 +4593,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>5</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>5</v>
@@ -4636,7 +4639,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>5</v>
@@ -4659,7 +4662,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>5</v>
@@ -4682,7 +4685,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>5</v>
@@ -4705,7 +4708,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>5</v>
@@ -4728,7 +4731,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>5</v>
@@ -4751,7 +4754,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>5</v>
@@ -4774,7 +4777,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>5</v>
@@ -4797,7 +4800,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>5</v>
@@ -4820,7 +4823,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>5</v>
@@ -4843,7 +4846,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>5</v>
@@ -4866,7 +4869,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>5</v>
@@ -4889,7 +4892,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>5</v>
@@ -4912,7 +4915,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>5</v>
@@ -4935,7 +4938,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>5</v>
@@ -4958,7 +4961,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>5</v>
@@ -4981,7 +4984,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>5</v>
@@ -5004,7 +5007,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>5</v>
@@ -5027,7 +5030,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>6</v>
@@ -5050,7 +5053,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>6</v>
@@ -5073,7 +5076,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>6</v>
@@ -5096,7 +5099,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>6</v>
@@ -5119,7 +5122,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>6</v>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>6</v>
@@ -5165,7 +5168,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>6</v>
@@ -5188,7 +5191,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>6</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>6</v>
@@ -5234,7 +5237,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>6</v>
@@ -5257,7 +5260,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>6</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>6</v>
@@ -5303,7 +5306,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>6</v>
@@ -5326,7 +5329,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>6</v>
@@ -5349,7 +5352,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>6</v>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>6</v>
@@ -5395,7 +5398,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>6</v>
@@ -5418,7 +5421,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>6</v>
@@ -5441,7 +5444,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>6</v>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>6</v>
@@ -5487,7 +5490,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>6</v>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>6</v>
@@ -5533,7 +5536,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>6</v>
@@ -5556,7 +5559,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>6</v>
@@ -5579,7 +5582,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>6</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>6</v>
@@ -5625,7 +5628,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>6</v>
@@ -5648,7 +5651,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>6</v>
@@ -5671,7 +5674,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>6</v>
@@ -5694,7 +5697,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>6</v>
@@ -5717,7 +5720,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>6</v>
@@ -5740,7 +5743,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>6</v>
@@ -5763,7 +5766,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>7</v>
@@ -5786,7 +5789,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>7</v>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>7</v>
@@ -5832,7 +5835,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>7</v>
@@ -5855,7 +5858,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>7</v>
@@ -5878,7 +5881,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>7</v>
@@ -5901,7 +5904,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>7</v>
@@ -5924,7 +5927,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>7</v>
@@ -5947,7 +5950,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>7</v>
@@ -5970,7 +5973,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>7</v>
@@ -5993,7 +5996,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>7</v>
@@ -6016,7 +6019,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>7</v>
@@ -6039,7 +6042,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>7</v>
@@ -6062,7 +6065,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>7</v>
@@ -6085,7 +6088,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>7</v>
@@ -6108,7 +6111,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>7</v>
@@ -6131,7 +6134,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>7</v>
@@ -6154,7 +6157,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>7</v>
@@ -6177,7 +6180,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>7</v>
@@ -6200,7 +6203,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>7</v>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>7</v>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>7</v>
@@ -6269,7 +6272,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>7</v>
@@ -6292,7 +6295,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>7</v>
@@ -6315,7 +6318,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>7</v>
@@ -6338,7 +6341,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>7</v>
@@ -6361,7 +6364,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>7</v>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>7</v>
@@ -6407,7 +6410,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>7</v>
@@ -6430,7 +6433,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>7</v>
@@ -6453,7 +6456,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>7</v>
@@ -6476,7 +6479,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>7</v>
@@ -6499,7 +6502,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>8</v>
@@ -6522,7 +6525,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>8</v>
@@ -6545,7 +6548,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>8</v>
@@ -6568,7 +6571,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>8</v>
@@ -6591,7 +6594,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>8</v>
@@ -6614,7 +6617,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>8</v>
@@ -6637,7 +6640,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>8</v>
@@ -6660,7 +6663,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>8</v>
@@ -6683,7 +6686,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>8</v>
@@ -6706,7 +6709,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>8</v>
@@ -6729,7 +6732,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>8</v>
@@ -6752,7 +6755,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>8</v>
@@ -6775,7 +6778,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>8</v>
@@ -6798,7 +6801,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>8</v>
@@ -6821,7 +6824,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>8</v>
@@ -6844,7 +6847,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>8</v>
@@ -6867,7 +6870,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>8</v>
@@ -6890,7 +6893,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>8</v>
@@ -6913,7 +6916,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>8</v>
@@ -6936,7 +6939,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>8</v>
@@ -6959,7 +6962,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>8</v>
@@ -6982,7 +6985,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>8</v>
@@ -7005,7 +7008,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>8</v>
@@ -7028,7 +7031,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>8</v>
@@ -7051,7 +7054,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>8</v>
@@ -7074,7 +7077,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>8</v>
@@ -7097,7 +7100,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>8</v>
@@ -7120,7 +7123,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>8</v>
@@ -7143,7 +7146,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>8</v>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>8</v>
@@ -7189,7 +7192,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>8</v>
@@ -7212,7 +7215,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>8</v>
@@ -7235,7 +7238,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>9</v>
@@ -7258,7 +7261,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>9</v>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>9</v>
@@ -7304,7 +7307,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>9</v>
@@ -7327,7 +7330,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>9</v>
@@ -7350,7 +7353,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>9</v>
@@ -7373,7 +7376,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>9</v>
@@ -7396,7 +7399,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>9</v>
@@ -7419,7 +7422,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>9</v>
@@ -7442,7 +7445,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>9</v>
@@ -7465,7 +7468,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>9</v>
@@ -7488,7 +7491,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>9</v>
@@ -7511,7 +7514,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>9</v>
@@ -7534,7 +7537,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>9</v>
@@ -7557,7 +7560,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>9</v>
@@ -7580,7 +7583,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>9</v>
@@ -7603,7 +7606,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>9</v>
@@ -7626,7 +7629,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>9</v>
@@ -7649,7 +7652,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>9</v>
@@ -7672,7 +7675,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>9</v>
@@ -7695,7 +7698,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>9</v>
@@ -7718,7 +7721,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>9</v>
@@ -7741,7 +7744,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>9</v>
@@ -7764,7 +7767,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>9</v>
@@ -7787,7 +7790,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>9</v>
@@ -7810,7 +7813,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>9</v>
@@ -7833,7 +7836,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>9</v>
@@ -7856,7 +7859,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>9</v>
@@ -7879,7 +7882,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>9</v>
@@ -7902,7 +7905,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>9</v>
@@ -7925,7 +7928,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>9</v>
@@ -7948,7 +7951,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>9</v>
@@ -7971,7 +7974,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>10</v>
@@ -7994,7 +7997,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>10</v>
@@ -8017,7 +8020,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>10</v>
@@ -8040,7 +8043,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>10</v>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>10</v>
@@ -8086,7 +8089,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>10</v>
@@ -8109,7 +8112,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>10</v>
@@ -8132,7 +8135,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>10</v>
@@ -8155,7 +8158,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>10</v>
@@ -8178,7 +8181,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>10</v>
@@ -8201,7 +8204,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>10</v>
@@ -8224,7 +8227,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>10</v>
@@ -8247,7 +8250,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>10</v>
@@ -8270,7 +8273,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>10</v>
@@ -8293,7 +8296,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>10</v>
@@ -8316,7 +8319,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>10</v>
@@ -8339,7 +8342,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>10</v>
@@ -8362,7 +8365,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>10</v>
@@ -8385,7 +8388,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>10</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>10</v>
@@ -8431,7 +8434,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>10</v>
@@ -8454,7 +8457,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>10</v>
@@ -8477,7 +8480,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>10</v>
@@ -8500,7 +8503,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>10</v>
@@ -8523,7 +8526,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>10</v>
@@ -8546,7 +8549,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>10</v>
@@ -8569,7 +8572,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>10</v>
@@ -8592,7 +8595,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>10</v>
@@ -8615,7 +8618,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>10</v>
@@ -8638,7 +8641,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>10</v>
@@ -8661,7 +8664,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>10</v>
@@ -8684,7 +8687,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>10</v>
@@ -8707,7 +8710,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>11</v>
@@ -8730,7 +8733,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>11</v>
@@ -8753,7 +8756,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>11</v>
@@ -8776,7 +8779,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>11</v>
@@ -8799,7 +8802,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>11</v>
@@ -8822,7 +8825,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>11</v>
@@ -8845,7 +8848,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>11</v>
@@ -8868,7 +8871,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>11</v>
@@ -8891,7 +8894,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>11</v>
@@ -8914,7 +8917,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>11</v>
@@ -8937,7 +8940,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>11</v>
@@ -8960,7 +8963,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>11</v>
@@ -8983,7 +8986,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>11</v>
@@ -9006,7 +9009,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>11</v>
@@ -9029,7 +9032,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>11</v>
@@ -9052,7 +9055,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>11</v>
@@ -9075,7 +9078,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>11</v>
@@ -9098,7 +9101,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>11</v>
@@ -9121,7 +9124,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>11</v>
@@ -9144,7 +9147,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>11</v>
@@ -9167,7 +9170,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>11</v>
@@ -9190,7 +9193,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>11</v>
@@ -9213,7 +9216,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>11</v>
@@ -9236,7 +9239,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>11</v>
@@ -9259,7 +9262,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>11</v>
@@ -9282,7 +9285,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>11</v>
@@ -9305,7 +9308,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>11</v>
@@ -9328,7 +9331,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>11</v>
@@ -9351,7 +9354,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>11</v>
@@ -9374,7 +9377,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>11</v>
@@ -9397,7 +9400,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>11</v>
@@ -9420,7 +9423,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>11</v>
@@ -9443,7 +9446,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>12</v>
@@ -9466,7 +9469,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>12</v>
@@ -9489,7 +9492,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>12</v>
@@ -9512,7 +9515,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>12</v>
@@ -9535,7 +9538,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>12</v>
@@ -9558,7 +9561,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>12</v>
@@ -9581,7 +9584,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>12</v>
@@ -9604,7 +9607,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>12</v>
@@ -9627,7 +9630,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>12</v>
@@ -9650,7 +9653,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>12</v>
@@ -9673,7 +9676,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>12</v>
@@ -9696,7 +9699,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>12</v>
@@ -9719,7 +9722,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>12</v>
@@ -9742,7 +9745,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>12</v>
@@ -9765,7 +9768,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>12</v>
@@ -9788,7 +9791,7 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>12</v>
@@ -9811,7 +9814,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>12</v>
@@ -9834,7 +9837,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>12</v>
@@ -9857,7 +9860,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>12</v>
@@ -9880,7 +9883,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>12</v>
@@ -9903,7 +9906,7 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>12</v>
@@ -9926,7 +9929,7 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>12</v>
@@ -9949,7 +9952,7 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>12</v>
@@ -9972,7 +9975,7 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>12</v>
@@ -9995,7 +9998,7 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>12</v>
@@ -10018,7 +10021,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>12</v>
@@ -10041,7 +10044,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>12</v>
@@ -10064,7 +10067,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>12</v>
@@ -10087,7 +10090,7 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>12</v>
@@ -10110,7 +10113,7 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>12</v>
@@ -10133,7 +10136,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>12</v>
@@ -10156,7 +10159,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>12</v>
@@ -10179,7 +10182,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>13</v>
@@ -10202,7 +10205,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>13</v>
@@ -10225,7 +10228,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>13</v>
@@ -10248,7 +10251,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>13</v>
@@ -10271,7 +10274,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>13</v>
@@ -10294,7 +10297,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>13</v>
@@ -10317,7 +10320,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>13</v>
@@ -10340,7 +10343,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>13</v>
@@ -10363,7 +10366,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>13</v>
@@ -10386,7 +10389,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>13</v>
@@ -10409,7 +10412,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>13</v>
@@ -10432,7 +10435,7 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>13</v>
@@ -10455,7 +10458,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>13</v>
@@ -10478,7 +10481,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>13</v>
@@ -10501,7 +10504,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>13</v>
@@ -10524,7 +10527,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>13</v>
@@ -10547,7 +10550,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>13</v>
@@ -10570,7 +10573,7 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>13</v>
@@ -10593,7 +10596,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>13</v>
@@ -10616,7 +10619,7 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>13</v>
@@ -10639,7 +10642,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>13</v>
@@ -10662,7 +10665,7 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>13</v>
@@ -10685,7 +10688,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>13</v>
@@ -10708,7 +10711,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>13</v>
@@ -10731,7 +10734,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>13</v>
@@ -10754,7 +10757,7 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>13</v>
@@ -10777,7 +10780,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>13</v>
@@ -10800,7 +10803,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>13</v>
@@ -10823,7 +10826,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>13</v>
@@ -10846,7 +10849,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>13</v>
@@ -10869,7 +10872,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>13</v>
@@ -10892,7 +10895,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>13</v>
@@ -10915,7 +10918,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>14</v>
@@ -10938,7 +10941,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>14</v>
@@ -10961,7 +10964,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>14</v>
@@ -10984,7 +10987,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>14</v>
@@ -11007,7 +11010,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>14</v>
@@ -11030,7 +11033,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>14</v>
@@ -11053,7 +11056,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>14</v>
@@ -11076,7 +11079,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>14</v>
@@ -11099,7 +11102,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>14</v>
@@ -11122,7 +11125,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>14</v>
@@ -11145,7 +11148,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>14</v>
@@ -11168,7 +11171,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>14</v>
@@ -11191,7 +11194,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>14</v>
@@ -11214,7 +11217,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>14</v>
@@ -11237,7 +11240,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>14</v>
@@ -11260,7 +11263,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>14</v>
@@ -11283,7 +11286,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>14</v>
@@ -11306,7 +11309,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>14</v>
@@ -11329,7 +11332,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>14</v>
@@ -11352,7 +11355,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>14</v>
@@ -11375,7 +11378,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>14</v>
@@ -11398,7 +11401,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>14</v>
@@ -11421,7 +11424,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>14</v>
@@ -11444,7 +11447,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>14</v>
@@ -11467,7 +11470,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>14</v>
@@ -11490,7 +11493,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>14</v>
@@ -11513,7 +11516,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>14</v>
@@ -11536,7 +11539,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>14</v>
@@ -11559,7 +11562,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>14</v>
@@ -11582,7 +11585,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>14</v>
@@ -11605,7 +11608,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>14</v>
@@ -11628,7 +11631,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>14</v>
@@ -11651,7 +11654,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>15</v>
@@ -11674,7 +11677,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>15</v>
@@ -11697,7 +11700,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>15</v>
@@ -11720,7 +11723,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>15</v>
@@ -11743,7 +11746,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>15</v>
@@ -11766,7 +11769,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>15</v>
@@ -11789,7 +11792,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>15</v>
@@ -11812,7 +11815,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>15</v>
@@ -11835,7 +11838,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>15</v>
@@ -11858,7 +11861,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>15</v>
@@ -11881,7 +11884,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>15</v>
@@ -11904,7 +11907,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>15</v>
@@ -11927,7 +11930,7 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>15</v>
@@ -11950,7 +11953,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>15</v>
@@ -11973,7 +11976,7 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>15</v>
@@ -11996,7 +11999,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>15</v>
@@ -12019,7 +12022,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>15</v>
@@ -12042,7 +12045,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>15</v>
@@ -12065,7 +12068,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>15</v>
@@ -12088,7 +12091,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>15</v>
@@ -12111,7 +12114,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>15</v>
@@ -12134,7 +12137,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>15</v>
@@ -12157,7 +12160,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>15</v>
@@ -12180,7 +12183,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>15</v>
@@ -12203,7 +12206,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>15</v>
@@ -12226,7 +12229,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>15</v>
@@ -12249,7 +12252,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>15</v>
@@ -12272,7 +12275,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>15</v>
@@ -12295,7 +12298,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>15</v>
@@ -12318,7 +12321,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>15</v>
@@ -12341,7 +12344,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>15</v>
@@ -12364,7 +12367,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>15</v>
@@ -12387,7 +12390,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>16</v>
@@ -12410,7 +12413,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>16</v>
@@ -12433,7 +12436,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>16</v>
@@ -12456,7 +12459,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>16</v>
@@ -12479,7 +12482,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>16</v>
@@ -12502,7 +12505,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>16</v>
@@ -12525,7 +12528,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>16</v>
@@ -12548,7 +12551,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>16</v>
@@ -12571,7 +12574,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>16</v>
@@ -12594,7 +12597,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>16</v>
@@ -12617,7 +12620,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>16</v>
@@ -12640,7 +12643,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>16</v>
@@ -12663,7 +12666,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>16</v>
@@ -12686,7 +12689,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>16</v>
@@ -12709,7 +12712,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>16</v>
@@ -12732,7 +12735,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>16</v>
@@ -12755,7 +12758,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>16</v>
@@ -12778,7 +12781,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>16</v>
@@ -12801,7 +12804,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>16</v>
@@ -12824,7 +12827,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>16</v>
@@ -12847,7 +12850,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>16</v>
@@ -12870,7 +12873,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>16</v>
@@ -12893,7 +12896,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>16</v>
@@ -12916,7 +12919,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>16</v>
@@ -12939,7 +12942,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>16</v>
@@ -12962,7 +12965,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>16</v>
@@ -12985,7 +12988,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>16</v>
@@ -13008,7 +13011,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>16</v>
@@ -13031,7 +13034,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>16</v>
@@ -13054,7 +13057,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>16</v>
@@ -13077,7 +13080,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>16</v>
@@ -13100,7 +13103,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>16</v>
@@ -13123,7 +13126,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>17</v>
@@ -13146,7 +13149,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>17</v>
@@ -13169,7 +13172,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>17</v>
@@ -13192,7 +13195,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>17</v>
@@ -13215,7 +13218,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>17</v>
@@ -13238,7 +13241,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>17</v>
@@ -13261,7 +13264,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>17</v>
@@ -13284,7 +13287,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>17</v>
@@ -13307,7 +13310,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>17</v>
@@ -13330,7 +13333,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>17</v>
@@ -13353,7 +13356,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>17</v>
@@ -13376,7 +13379,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>17</v>
@@ -13399,7 +13402,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>17</v>
@@ -13422,7 +13425,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>17</v>
@@ -13445,7 +13448,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>17</v>
@@ -13468,7 +13471,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>17</v>
@@ -13491,7 +13494,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>17</v>
@@ -13514,7 +13517,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>17</v>
@@ -13537,7 +13540,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>17</v>
@@ -13560,7 +13563,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>17</v>
@@ -13583,7 +13586,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>17</v>
@@ -13606,7 +13609,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>17</v>
@@ -13629,7 +13632,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>17</v>
@@ -13652,7 +13655,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>17</v>
@@ -13675,7 +13678,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>17</v>
@@ -13698,7 +13701,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>17</v>
@@ -13721,7 +13724,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>17</v>
@@ -13744,7 +13747,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>17</v>
@@ -13767,7 +13770,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>17</v>
@@ -13790,7 +13793,7 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>17</v>
@@ -13813,7 +13816,7 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>17</v>
@@ -13836,7 +13839,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>17</v>
@@ -13859,7 +13862,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>18</v>
@@ -13882,7 +13885,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>18</v>
@@ -13905,7 +13908,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>18</v>
@@ -13928,7 +13931,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>18</v>
@@ -13951,7 +13954,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>18</v>
@@ -13974,7 +13977,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>18</v>
@@ -13997,7 +14000,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>18</v>
@@ -14020,7 +14023,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>18</v>
@@ -14043,7 +14046,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>18</v>
@@ -14066,7 +14069,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>18</v>
@@ -14089,7 +14092,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>18</v>
@@ -14112,7 +14115,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>18</v>
@@ -14135,7 +14138,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>18</v>
@@ -14158,7 +14161,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>18</v>
@@ -14181,7 +14184,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>18</v>
@@ -14204,7 +14207,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>18</v>
@@ -14227,7 +14230,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>18</v>
@@ -14250,7 +14253,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>18</v>
@@ -14273,7 +14276,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>18</v>
@@ -14296,7 +14299,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>18</v>
@@ -14319,7 +14322,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>18</v>
@@ -14342,7 +14345,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>18</v>
@@ -14365,7 +14368,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>18</v>
@@ -14388,7 +14391,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>18</v>
@@ -14411,7 +14414,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>18</v>
@@ -14434,7 +14437,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>18</v>
@@ -14457,7 +14460,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>18</v>
@@ -14480,7 +14483,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>18</v>
@@ -14503,7 +14506,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>18</v>
@@ -14526,7 +14529,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>18</v>
@@ -14549,7 +14552,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>18</v>
@@ -14572,7 +14575,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>18</v>
@@ -14595,7 +14598,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>19</v>
@@ -14618,7 +14621,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>19</v>
@@ -14641,7 +14644,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>19</v>
@@ -14664,7 +14667,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>19</v>
@@ -14687,7 +14690,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>19</v>
@@ -14710,7 +14713,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>19</v>
@@ -14733,7 +14736,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>19</v>
@@ -14756,7 +14759,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>19</v>
@@ -14779,7 +14782,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>19</v>
@@ -14802,7 +14805,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>19</v>
@@ -14825,7 +14828,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>19</v>
@@ -14848,7 +14851,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>19</v>
@@ -14871,7 +14874,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>19</v>
@@ -14894,7 +14897,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>19</v>
@@ -14917,7 +14920,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>19</v>
@@ -14940,7 +14943,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>19</v>
@@ -14963,7 +14966,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>19</v>
@@ -14986,7 +14989,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>19</v>
@@ -15009,7 +15012,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>19</v>
@@ -15032,7 +15035,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>19</v>
@@ -15055,7 +15058,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>19</v>
@@ -15078,7 +15081,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>19</v>
@@ -15101,7 +15104,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>19</v>
@@ -15124,7 +15127,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>19</v>
@@ -15147,7 +15150,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>19</v>
@@ -15170,7 +15173,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>19</v>
@@ -15193,7 +15196,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>19</v>
@@ -15216,7 +15219,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>19</v>
@@ -15239,7 +15242,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>19</v>
@@ -15262,7 +15265,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>19</v>
@@ -15285,7 +15288,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>19</v>
@@ -15308,7 +15311,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>19</v>
@@ -15331,7 +15334,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>20</v>
@@ -15354,7 +15357,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>20</v>
@@ -15377,7 +15380,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>20</v>
@@ -15400,7 +15403,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>20</v>
@@ -15423,7 +15426,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>20</v>
@@ -15446,7 +15449,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>20</v>
@@ -15469,7 +15472,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>20</v>
@@ -15492,7 +15495,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>20</v>
@@ -15515,7 +15518,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>20</v>
@@ -15538,7 +15541,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B523" s="3" t="s">
         <v>20</v>
@@ -15561,7 +15564,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B524" s="3" t="s">
         <v>20</v>
@@ -15584,7 +15587,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B525" s="3" t="s">
         <v>20</v>
@@ -15607,7 +15610,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>20</v>
@@ -15630,7 +15633,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>20</v>
@@ -15653,7 +15656,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>20</v>
@@ -15676,7 +15679,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>20</v>
@@ -15699,7 +15702,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>20</v>
@@ -15722,7 +15725,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>20</v>
@@ -15745,7 +15748,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>20</v>
@@ -15768,7 +15771,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>20</v>
@@ -15791,7 +15794,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B534" s="3" t="s">
         <v>20</v>
@@ -15814,7 +15817,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>20</v>
@@ -15837,7 +15840,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>20</v>
@@ -15860,7 +15863,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B537" s="3" t="s">
         <v>20</v>
@@ -15883,7 +15886,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B538" s="3" t="s">
         <v>20</v>
@@ -15906,7 +15909,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B539" s="3" t="s">
         <v>20</v>
@@ -15929,7 +15932,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>20</v>
@@ -15952,7 +15955,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>20</v>
@@ -15975,7 +15978,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>20</v>
@@ -15998,7 +16001,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>20</v>
@@ -16021,7 +16024,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>20</v>
@@ -16044,7 +16047,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>20</v>
@@ -16067,7 +16070,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>21</v>
@@ -16090,7 +16093,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B547" s="3" t="s">
         <v>21</v>
@@ -16113,7 +16116,7 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>21</v>
@@ -16136,7 +16139,7 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>21</v>
@@ -16159,7 +16162,7 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>21</v>
@@ -16182,7 +16185,7 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>21</v>
@@ -16205,7 +16208,7 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>21</v>
@@ -16228,7 +16231,7 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>21</v>
@@ -16251,7 +16254,7 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>21</v>
@@ -16274,7 +16277,7 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>21</v>
@@ -16297,7 +16300,7 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>21</v>
@@ -16320,7 +16323,7 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>21</v>
@@ -16343,7 +16346,7 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>21</v>
@@ -16366,7 +16369,7 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>21</v>
@@ -16389,7 +16392,7 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>21</v>
@@ -16412,7 +16415,7 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>21</v>
@@ -16435,7 +16438,7 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>21</v>
@@ -16458,7 +16461,7 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>21</v>
@@ -16481,7 +16484,7 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B564" s="3" t="s">
         <v>21</v>
@@ -16504,7 +16507,7 @@
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>21</v>
@@ -16527,7 +16530,7 @@
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B566" s="3" t="s">
         <v>21</v>
@@ -16550,7 +16553,7 @@
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B567" s="3" t="s">
         <v>21</v>
@@ -16573,7 +16576,7 @@
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B568" s="3" t="s">
         <v>21</v>
@@ -16596,7 +16599,7 @@
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>21</v>
@@ -16619,7 +16622,7 @@
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B570" s="3" t="s">
         <v>21</v>
@@ -16642,7 +16645,7 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B571" s="3" t="s">
         <v>21</v>
@@ -16665,7 +16668,7 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>21</v>
@@ -16688,7 +16691,7 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B573" s="3" t="s">
         <v>21</v>
@@ -16711,7 +16714,7 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>21</v>
@@ -16734,7 +16737,7 @@
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B575" s="3" t="s">
         <v>21</v>
@@ -16757,7 +16760,7 @@
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>21</v>
@@ -16780,7 +16783,7 @@
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>21</v>
@@ -16803,7 +16806,7 @@
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>22</v>
@@ -16826,7 +16829,7 @@
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B579" s="3" t="s">
         <v>22</v>
@@ -16849,7 +16852,7 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B580" s="3" t="s">
         <v>22</v>
@@ -16872,7 +16875,7 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>22</v>
@@ -16895,7 +16898,7 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B582" s="3" t="s">
         <v>22</v>
@@ -16918,7 +16921,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>22</v>
@@ -16941,7 +16944,7 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B584" s="3" t="s">
         <v>22</v>
@@ -16964,7 +16967,7 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B585" s="3" t="s">
         <v>22</v>
@@ -16987,7 +16990,7 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B586" s="3" t="s">
         <v>22</v>
@@ -17010,7 +17013,7 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>22</v>
@@ -17033,7 +17036,7 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>22</v>
@@ -17056,7 +17059,7 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>22</v>
@@ -17079,7 +17082,7 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B590" s="3" t="s">
         <v>22</v>
@@ -17102,7 +17105,7 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>22</v>
@@ -17125,7 +17128,7 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>22</v>
@@ -17148,7 +17151,7 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>22</v>
@@ -17171,7 +17174,7 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B594" s="3" t="s">
         <v>22</v>
@@ -17194,7 +17197,7 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B595" s="3" t="s">
         <v>22</v>
@@ -17217,7 +17220,7 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B596" s="3" t="s">
         <v>22</v>
@@ -17240,7 +17243,7 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B597" s="3" t="s">
         <v>22</v>
@@ -17263,7 +17266,7 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B598" s="3" t="s">
         <v>22</v>
@@ -17286,7 +17289,7 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B599" s="3" t="s">
         <v>22</v>
@@ -17309,7 +17312,7 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B600" s="3" t="s">
         <v>22</v>
@@ -17332,7 +17335,7 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B601" s="3" t="s">
         <v>22</v>
@@ -17355,7 +17358,7 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B602" s="3" t="s">
         <v>22</v>
@@ -17378,7 +17381,7 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B603" s="3" t="s">
         <v>22</v>
@@ -17401,7 +17404,7 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B604" s="3" t="s">
         <v>22</v>
@@ -17424,7 +17427,7 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>22</v>
@@ -17447,7 +17450,7 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B606" s="3" t="s">
         <v>22</v>
@@ -17470,7 +17473,7 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>22</v>
@@ -17493,7 +17496,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>22</v>
@@ -17516,7 +17519,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B609" s="3" t="s">
         <v>22</v>
@@ -17539,7 +17542,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>23</v>
@@ -17562,7 +17565,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B611" s="3" t="s">
         <v>23</v>
@@ -17585,7 +17588,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B612" s="3" t="s">
         <v>23</v>
@@ -17608,7 +17611,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>23</v>
@@ -17631,7 +17634,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>23</v>
@@ -17654,7 +17657,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>23</v>
@@ -17677,7 +17680,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>23</v>
@@ -17700,7 +17703,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>23</v>
@@ -17723,7 +17726,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>23</v>
@@ -17746,7 +17749,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B619" s="3" t="s">
         <v>23</v>
@@ -17769,7 +17772,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>23</v>
@@ -17792,7 +17795,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>23</v>
@@ -17815,7 +17818,7 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>23</v>
@@ -17838,7 +17841,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>23</v>
@@ -17861,7 +17864,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B624" s="3" t="s">
         <v>23</v>
@@ -17884,7 +17887,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B625" s="3" t="s">
         <v>23</v>
@@ -17907,7 +17910,7 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>23</v>
@@ -17930,7 +17933,7 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B627" s="3" t="s">
         <v>23</v>
@@ -17953,7 +17956,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B628" s="3" t="s">
         <v>23</v>
@@ -17976,7 +17979,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B629" s="3" t="s">
         <v>23</v>
@@ -17999,7 +18002,7 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>23</v>
@@ -18022,7 +18025,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>23</v>
@@ -18045,7 +18048,7 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B632" s="3" t="s">
         <v>23</v>
@@ -18068,7 +18071,7 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B633" s="3" t="s">
         <v>23</v>
@@ -18091,7 +18094,7 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>23</v>
@@ -18114,7 +18117,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B635" s="3" t="s">
         <v>23</v>
@@ -18137,7 +18140,7 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>23</v>
@@ -18160,7 +18163,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B637" s="3" t="s">
         <v>23</v>
@@ -18183,7 +18186,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B638" s="3" t="s">
         <v>23</v>
@@ -18206,7 +18209,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B639" s="3" t="s">
         <v>23</v>
@@ -18229,7 +18232,7 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B640" s="3" t="s">
         <v>23</v>
@@ -18252,7 +18255,7 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>23</v>
@@ -18275,7 +18278,7 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B642" s="3" t="s">
         <v>24</v>
@@ -18298,7 +18301,7 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B643" s="3" t="s">
         <v>24</v>
@@ -18321,7 +18324,7 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B644" s="3" t="s">
         <v>24</v>
@@ -18344,7 +18347,7 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B645" s="3" t="s">
         <v>24</v>
@@ -18367,7 +18370,7 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B646" s="3" t="s">
         <v>24</v>
@@ -18390,7 +18393,7 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B647" s="3" t="s">
         <v>24</v>
@@ -18413,7 +18416,7 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B648" s="3" t="s">
         <v>24</v>
@@ -18436,7 +18439,7 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B649" s="3" t="s">
         <v>24</v>
@@ -18459,7 +18462,7 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B650" s="3" t="s">
         <v>24</v>
@@ -18482,7 +18485,7 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B651" s="3" t="s">
         <v>24</v>
@@ -18505,7 +18508,7 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B652" s="3" t="s">
         <v>24</v>
@@ -18528,7 +18531,7 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B653" s="3" t="s">
         <v>24</v>
@@ -18551,7 +18554,7 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>24</v>
@@ -18574,7 +18577,7 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B655" s="3" t="s">
         <v>24</v>
@@ -18597,7 +18600,7 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B656" s="3" t="s">
         <v>24</v>
@@ -18620,7 +18623,7 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>24</v>
@@ -18643,7 +18646,7 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B658" s="3" t="s">
         <v>24</v>
@@ -18666,7 +18669,7 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>24</v>
@@ -18689,7 +18692,7 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>24</v>
@@ -18712,7 +18715,7 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B661" s="3" t="s">
         <v>24</v>
@@ -18735,7 +18738,7 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B662" s="3" t="s">
         <v>24</v>
@@ -18758,7 +18761,7 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>24</v>
@@ -18781,7 +18784,7 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B664" s="3" t="s">
         <v>24</v>
@@ -18804,7 +18807,7 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B665" s="3" t="s">
         <v>24</v>
@@ -18827,7 +18830,7 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B666" s="3" t="s">
         <v>24</v>
@@ -18850,7 +18853,7 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>24</v>
@@ -18873,7 +18876,7 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B668" s="3" t="s">
         <v>24</v>
@@ -18896,7 +18899,7 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B669" s="3" t="s">
         <v>24</v>
@@ -18919,7 +18922,7 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B670" s="3" t="s">
         <v>24</v>
@@ -18942,7 +18945,7 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B671" s="3" t="s">
         <v>24</v>
@@ -18965,7 +18968,7 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B672" s="3" t="s">
         <v>24</v>
@@ -18988,7 +18991,7 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>24</v>
@@ -19011,7 +19014,7 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>25</v>
@@ -19034,7 +19037,7 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>25</v>
@@ -19057,7 +19060,7 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>25</v>
@@ -19080,7 +19083,7 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>25</v>
@@ -19103,7 +19106,7 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>25</v>
@@ -19126,7 +19129,7 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B679" s="3" t="s">
         <v>25</v>
@@ -19149,7 +19152,7 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B680" s="3" t="s">
         <v>25</v>
@@ -19172,7 +19175,7 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B681" s="3" t="s">
         <v>25</v>
@@ -19195,7 +19198,7 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>25</v>
@@ -19218,7 +19221,7 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B683" s="3" t="s">
         <v>25</v>
@@ -19241,7 +19244,7 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B684" s="3" t="s">
         <v>25</v>
@@ -19264,7 +19267,7 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B685" s="3" t="s">
         <v>25</v>
@@ -19287,7 +19290,7 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B686" s="3" t="s">
         <v>25</v>
@@ -19310,7 +19313,7 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B687" s="3" t="s">
         <v>25</v>
@@ -19333,7 +19336,7 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B688" s="3" t="s">
         <v>25</v>
@@ -19356,7 +19359,7 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B689" s="3" t="s">
         <v>25</v>
@@ -19379,7 +19382,7 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B690" s="3" t="s">
         <v>25</v>
@@ -19402,7 +19405,7 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B691" s="3" t="s">
         <v>25</v>
@@ -19425,7 +19428,7 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B692" s="3" t="s">
         <v>25</v>
@@ -19448,7 +19451,7 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B693" s="3" t="s">
         <v>25</v>
@@ -19471,7 +19474,7 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B694" s="3" t="s">
         <v>25</v>
@@ -19494,7 +19497,7 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B695" s="3" t="s">
         <v>25</v>
@@ -19517,7 +19520,7 @@
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B696" s="3" t="s">
         <v>25</v>
@@ -19540,7 +19543,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B697" s="3" t="s">
         <v>25</v>
@@ -19563,7 +19566,7 @@
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B698" s="3" t="s">
         <v>25</v>
@@ -19586,7 +19589,7 @@
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B699" s="3" t="s">
         <v>25</v>
@@ -19609,7 +19612,7 @@
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B700" s="3" t="s">
         <v>25</v>
@@ -19632,7 +19635,7 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>25</v>
@@ -19655,7 +19658,7 @@
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>25</v>
@@ -19678,7 +19681,7 @@
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>25</v>
@@ -19701,7 +19704,7 @@
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>25</v>
@@ -19724,7 +19727,7 @@
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B705" s="3" t="s">
         <v>25</v>
@@ -19747,7 +19750,7 @@
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B706" s="3" t="s">
         <v>26</v>
@@ -19770,7 +19773,7 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B707" s="3" t="s">
         <v>26</v>
@@ -19793,7 +19796,7 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B708" s="3" t="s">
         <v>26</v>
@@ -19816,7 +19819,7 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B709" s="3" t="s">
         <v>26</v>
@@ -19839,7 +19842,7 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B710" s="3" t="s">
         <v>26</v>
@@ -19862,7 +19865,7 @@
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B711" s="3" t="s">
         <v>26</v>
@@ -19885,7 +19888,7 @@
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B712" s="3" t="s">
         <v>26</v>
@@ -19908,7 +19911,7 @@
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B713" s="3" t="s">
         <v>26</v>
@@ -19931,7 +19934,7 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B714" s="3" t="s">
         <v>26</v>
@@ -19954,7 +19957,7 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B715" s="3" t="s">
         <v>26</v>
@@ -19977,7 +19980,7 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B716" s="3" t="s">
         <v>26</v>
@@ -20000,7 +20003,7 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B717" s="3" t="s">
         <v>26</v>
@@ -20023,7 +20026,7 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B718" s="3" t="s">
         <v>26</v>
@@ -20046,7 +20049,7 @@
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B719" s="3" t="s">
         <v>26</v>
@@ -20069,7 +20072,7 @@
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B720" s="3" t="s">
         <v>26</v>
@@ -20092,7 +20095,7 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B721" s="3" t="s">
         <v>26</v>
@@ -20115,7 +20118,7 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B722" s="3" t="s">
         <v>26</v>
@@ -20138,7 +20141,7 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B723" s="3" t="s">
         <v>26</v>
@@ -20161,7 +20164,7 @@
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B724" s="3" t="s">
         <v>26</v>
@@ -20184,7 +20187,7 @@
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B725" s="3" t="s">
         <v>26</v>
@@ -20207,7 +20210,7 @@
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B726" s="3" t="s">
         <v>26</v>
@@ -20230,7 +20233,7 @@
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B727" s="3" t="s">
         <v>26</v>
@@ -20253,7 +20256,7 @@
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B728" s="3" t="s">
         <v>26</v>
@@ -20276,7 +20279,7 @@
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B729" s="3" t="s">
         <v>26</v>
@@ -20299,7 +20302,7 @@
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B730" s="3" t="s">
         <v>26</v>
@@ -20322,7 +20325,7 @@
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B731" s="3" t="s">
         <v>26</v>
@@ -20345,7 +20348,7 @@
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B732" s="3" t="s">
         <v>26</v>
@@ -20368,7 +20371,7 @@
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B733" s="3" t="s">
         <v>26</v>
@@ -20391,7 +20394,7 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B734" s="3" t="s">
         <v>26</v>
@@ -20414,7 +20417,7 @@
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B735" s="3" t="s">
         <v>26</v>
@@ -20437,7 +20440,7 @@
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B736" s="3" t="s">
         <v>26</v>
@@ -20460,7 +20463,7 @@
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B737" s="3" t="s">
         <v>26</v>
@@ -20483,7 +20486,7 @@
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B738" s="3" t="s">
         <v>27</v>
@@ -20506,7 +20509,7 @@
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B739" s="3" t="s">
         <v>27</v>
@@ -20529,7 +20532,7 @@
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B740" s="3" t="s">
         <v>27</v>
@@ -20552,7 +20555,7 @@
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B741" s="3" t="s">
         <v>27</v>
@@ -20575,7 +20578,7 @@
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B742" s="3" t="s">
         <v>27</v>
@@ -20598,7 +20601,7 @@
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B743" s="3" t="s">
         <v>27</v>
@@ -20621,7 +20624,7 @@
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B744" s="3" t="s">
         <v>27</v>
@@ -20644,7 +20647,7 @@
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B745" s="3" t="s">
         <v>27</v>
@@ -20667,7 +20670,7 @@
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B746" s="3" t="s">
         <v>27</v>
@@ -20690,7 +20693,7 @@
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B747" s="3" t="s">
         <v>27</v>
@@ -20713,7 +20716,7 @@
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B748" s="3" t="s">
         <v>27</v>
@@ -20736,7 +20739,7 @@
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B749" s="3" t="s">
         <v>27</v>
@@ -20759,7 +20762,7 @@
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B750" s="3" t="s">
         <v>27</v>
@@ -20782,7 +20785,7 @@
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B751" s="3" t="s">
         <v>27</v>
@@ -20805,7 +20808,7 @@
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B752" s="3" t="s">
         <v>27</v>
@@ -20828,7 +20831,7 @@
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B753" s="3" t="s">
         <v>27</v>
@@ -20851,7 +20854,7 @@
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B754" s="3" t="s">
         <v>27</v>
@@ -20874,7 +20877,7 @@
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B755" s="3" t="s">
         <v>27</v>
@@ -20897,7 +20900,7 @@
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B756" s="3" t="s">
         <v>27</v>
@@ -20920,7 +20923,7 @@
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B757" s="3" t="s">
         <v>27</v>
@@ -20943,7 +20946,7 @@
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B758" s="3" t="s">
         <v>27</v>
@@ -20966,7 +20969,7 @@
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B759" s="3" t="s">
         <v>27</v>
@@ -20989,7 +20992,7 @@
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B760" s="3" t="s">
         <v>27</v>
@@ -21012,7 +21015,7 @@
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B761" s="3" t="s">
         <v>27</v>
@@ -21035,7 +21038,7 @@
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B762" s="3" t="s">
         <v>27</v>
@@ -21058,7 +21061,7 @@
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B763" s="3" t="s">
         <v>27</v>
@@ -21081,7 +21084,7 @@
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B764" s="3" t="s">
         <v>27</v>
@@ -21104,7 +21107,7 @@
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B765" s="3" t="s">
         <v>27</v>
@@ -21127,7 +21130,7 @@
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B766" s="3" t="s">
         <v>27</v>
@@ -21150,7 +21153,7 @@
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B767" s="3" t="s">
         <v>27</v>
@@ -21173,7 +21176,7 @@
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B768" s="3" t="s">
         <v>27</v>
@@ -21196,7 +21199,7 @@
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B769" s="3" t="s">
         <v>27</v>
@@ -21219,7 +21222,7 @@
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B770" s="3" t="s">
         <v>28</v>
@@ -21242,7 +21245,7 @@
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B771" s="3" t="s">
         <v>28</v>
@@ -21265,7 +21268,7 @@
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B772" s="3" t="s">
         <v>28</v>
@@ -21288,7 +21291,7 @@
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B773" s="3" t="s">
         <v>28</v>
@@ -21311,7 +21314,7 @@
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B774" s="3" t="s">
         <v>28</v>
@@ -21334,7 +21337,7 @@
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B775" s="3" t="s">
         <v>28</v>
@@ -21357,7 +21360,7 @@
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B776" s="3" t="s">
         <v>28</v>
@@ -21380,7 +21383,7 @@
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B777" s="3" t="s">
         <v>28</v>
@@ -21403,7 +21406,7 @@
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B778" s="3" t="s">
         <v>28</v>
@@ -21426,7 +21429,7 @@
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B779" s="3" t="s">
         <v>28</v>
@@ -21449,7 +21452,7 @@
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B780" s="3" t="s">
         <v>28</v>
@@ -21472,7 +21475,7 @@
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B781" s="3" t="s">
         <v>28</v>
@@ -21495,7 +21498,7 @@
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B782" s="3" t="s">
         <v>28</v>
@@ -21518,7 +21521,7 @@
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B783" s="3" t="s">
         <v>28</v>
@@ -21541,7 +21544,7 @@
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B784" s="3" t="s">
         <v>28</v>
@@ -21564,7 +21567,7 @@
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B785" s="3" t="s">
         <v>28</v>
@@ -21587,7 +21590,7 @@
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B786" s="3" t="s">
         <v>28</v>
@@ -21610,7 +21613,7 @@
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B787" s="3" t="s">
         <v>28</v>
@@ -21633,7 +21636,7 @@
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B788" s="3" t="s">
         <v>28</v>
@@ -21656,7 +21659,7 @@
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B789" s="3" t="s">
         <v>28</v>
@@ -21679,7 +21682,7 @@
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B790" s="3" t="s">
         <v>28</v>
@@ -21702,7 +21705,7 @@
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B791" s="3" t="s">
         <v>28</v>
@@ -21725,7 +21728,7 @@
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B792" s="3" t="s">
         <v>28</v>
@@ -21748,7 +21751,7 @@
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B793" s="3" t="s">
         <v>28</v>
@@ -21771,7 +21774,7 @@
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B794" s="3" t="s">
         <v>28</v>
@@ -21794,7 +21797,7 @@
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B795" s="3" t="s">
         <v>28</v>
@@ -21817,7 +21820,7 @@
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B796" s="3" t="s">
         <v>28</v>
@@ -21840,7 +21843,7 @@
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B797" s="3" t="s">
         <v>28</v>
@@ -21863,7 +21866,7 @@
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B798" s="3" t="s">
         <v>28</v>
@@ -21886,7 +21889,7 @@
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B799" s="3" t="s">
         <v>28</v>
@@ -21909,7 +21912,7 @@
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B800" s="3" t="s">
         <v>28</v>
@@ -21932,7 +21935,7 @@
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B801" s="3" t="s">
         <v>28</v>
@@ -21955,7 +21958,7 @@
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B802" s="3" t="s">
         <v>29</v>
@@ -21978,7 +21981,7 @@
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B803" s="3" t="s">
         <v>29</v>
@@ -22001,7 +22004,7 @@
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A804" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B804" s="3" t="s">
         <v>29</v>
@@ -22024,7 +22027,7 @@
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B805" s="3" t="s">
         <v>29</v>
@@ -22047,7 +22050,7 @@
     </row>
     <row r="806" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B806" s="3" t="s">
         <v>29</v>
@@ -22070,7 +22073,7 @@
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B807" s="3" t="s">
         <v>29</v>
@@ -22093,7 +22096,7 @@
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B808" s="3" t="s">
         <v>29</v>
@@ -22116,7 +22119,7 @@
     </row>
     <row r="809" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B809" s="3" t="s">
         <v>29</v>
@@ -22139,7 +22142,7 @@
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B810" s="3" t="s">
         <v>29</v>
@@ -22162,7 +22165,7 @@
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B811" s="3" t="s">
         <v>29</v>
@@ -22185,7 +22188,7 @@
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B812" s="3" t="s">
         <v>29</v>
@@ -22208,7 +22211,7 @@
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B813" s="3" t="s">
         <v>29</v>
@@ -22231,7 +22234,7 @@
     </row>
     <row r="814" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B814" s="3" t="s">
         <v>29</v>
@@ -22254,7 +22257,7 @@
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B815" s="3" t="s">
         <v>29</v>
@@ -22277,7 +22280,7 @@
     </row>
     <row r="816" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B816" s="3" t="s">
         <v>29</v>
@@ -22300,7 +22303,7 @@
     </row>
     <row r="817" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B817" s="3" t="s">
         <v>29</v>
@@ -22323,7 +22326,7 @@
     </row>
     <row r="818" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B818" s="3" t="s">
         <v>29</v>
@@ -22346,7 +22349,7 @@
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B819" s="3" t="s">
         <v>29</v>
@@ -22369,7 +22372,7 @@
     </row>
     <row r="820" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B820" s="3" t="s">
         <v>29</v>
@@ -22392,7 +22395,7 @@
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B821" s="3" t="s">
         <v>29</v>
@@ -22415,7 +22418,7 @@
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B822" s="3" t="s">
         <v>29</v>
@@ -22438,7 +22441,7 @@
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B823" s="3" t="s">
         <v>29</v>
@@ -22461,7 +22464,7 @@
     </row>
     <row r="824" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B824" s="3" t="s">
         <v>29</v>
@@ -22484,7 +22487,7 @@
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B825" s="3" t="s">
         <v>29</v>
@@ -22507,7 +22510,7 @@
     </row>
     <row r="826" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B826" s="3" t="s">
         <v>29</v>
@@ -22530,7 +22533,7 @@
     </row>
     <row r="827" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B827" s="3" t="s">
         <v>29</v>
@@ -22553,7 +22556,7 @@
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B828" s="3" t="s">
         <v>29</v>
@@ -22576,7 +22579,7 @@
     </row>
     <row r="829" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B829" s="3" t="s">
         <v>29</v>
@@ -22599,7 +22602,7 @@
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B830" s="3" t="s">
         <v>29</v>
@@ -22622,7 +22625,7 @@
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B831" s="3" t="s">
         <v>29</v>
@@ -22645,7 +22648,7 @@
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B832" s="3" t="s">
         <v>29</v>
@@ -22668,7 +22671,7 @@
     </row>
     <row r="833" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B833" s="3" t="s">
         <v>29</v>
@@ -22691,7 +22694,7 @@
     </row>
     <row r="834" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B834" s="3" t="s">
         <v>30</v>
@@ -22714,7 +22717,7 @@
     </row>
     <row r="835" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B835" s="3" t="s">
         <v>30</v>
@@ -22737,7 +22740,7 @@
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B836" s="3" t="s">
         <v>30</v>
@@ -22760,7 +22763,7 @@
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B837" s="3" t="s">
         <v>30</v>
@@ -22783,7 +22786,7 @@
     </row>
     <row r="838" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B838" s="3" t="s">
         <v>30</v>
@@ -22806,7 +22809,7 @@
     </row>
     <row r="839" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B839" s="3" t="s">
         <v>30</v>
@@ -22829,7 +22832,7 @@
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B840" s="3" t="s">
         <v>30</v>
@@ -22852,7 +22855,7 @@
     </row>
     <row r="841" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B841" s="3" t="s">
         <v>30</v>
@@ -22875,7 +22878,7 @@
     </row>
     <row r="842" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B842" s="3" t="s">
         <v>30</v>
@@ -22898,7 +22901,7 @@
     </row>
     <row r="843" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B843" s="3" t="s">
         <v>30</v>
@@ -22921,7 +22924,7 @@
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B844" s="3" t="s">
         <v>30</v>
@@ -22944,7 +22947,7 @@
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B845" s="3" t="s">
         <v>30</v>
@@ -22967,7 +22970,7 @@
     </row>
     <row r="846" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B846" s="3" t="s">
         <v>30</v>
@@ -22990,7 +22993,7 @@
     </row>
     <row r="847" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B847" s="3" t="s">
         <v>30</v>
@@ -23013,7 +23016,7 @@
     </row>
     <row r="848" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B848" s="3" t="s">
         <v>30</v>
@@ -23036,7 +23039,7 @@
     </row>
     <row r="849" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B849" s="3" t="s">
         <v>30</v>
@@ -23059,7 +23062,7 @@
     </row>
     <row r="850" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B850" s="3" t="s">
         <v>30</v>
@@ -23082,7 +23085,7 @@
     </row>
     <row r="851" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B851" s="3" t="s">
         <v>30</v>
@@ -23105,7 +23108,7 @@
     </row>
     <row r="852" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B852" s="3" t="s">
         <v>30</v>
@@ -23128,7 +23131,7 @@
     </row>
     <row r="853" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B853" s="3" t="s">
         <v>30</v>
@@ -23151,7 +23154,7 @@
     </row>
     <row r="854" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B854" s="3" t="s">
         <v>30</v>
@@ -23174,7 +23177,7 @@
     </row>
     <row r="855" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B855" s="3" t="s">
         <v>30</v>
@@ -23197,7 +23200,7 @@
     </row>
     <row r="856" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B856" s="3" t="s">
         <v>30</v>
@@ -23220,7 +23223,7 @@
     </row>
     <row r="857" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B857" s="3" t="s">
         <v>30</v>
@@ -23243,7 +23246,7 @@
     </row>
     <row r="858" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B858" s="3" t="s">
         <v>30</v>
@@ -23266,7 +23269,7 @@
     </row>
     <row r="859" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B859" s="3" t="s">
         <v>30</v>
@@ -23289,7 +23292,7 @@
     </row>
     <row r="860" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B860" s="3" t="s">
         <v>30</v>
@@ -23312,7 +23315,7 @@
     </row>
     <row r="861" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B861" s="3" t="s">
         <v>30</v>
@@ -23335,7 +23338,7 @@
     </row>
     <row r="862" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B862" s="3" t="s">
         <v>30</v>
@@ -23358,7 +23361,7 @@
     </row>
     <row r="863" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B863" s="3" t="s">
         <v>30</v>
@@ -23381,7 +23384,7 @@
     </row>
     <row r="864" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B864" s="3" t="s">
         <v>30</v>
@@ -23404,7 +23407,7 @@
     </row>
     <row r="865" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B865" s="3" t="s">
         <v>30</v>
@@ -23427,7 +23430,7 @@
     </row>
     <row r="866" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B866" s="3" t="s">
         <v>31</v>
@@ -23450,7 +23453,7 @@
     </row>
     <row r="867" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B867" s="3" t="s">
         <v>31</v>
@@ -23473,7 +23476,7 @@
     </row>
     <row r="868" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B868" s="3" t="s">
         <v>31</v>
@@ -23496,7 +23499,7 @@
     </row>
     <row r="869" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B869" s="3" t="s">
         <v>31</v>
@@ -23519,7 +23522,7 @@
     </row>
     <row r="870" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B870" s="3" t="s">
         <v>31</v>
@@ -23542,7 +23545,7 @@
     </row>
     <row r="871" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B871" s="3" t="s">
         <v>31</v>
@@ -23565,7 +23568,7 @@
     </row>
     <row r="872" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B872" s="3" t="s">
         <v>31</v>
@@ -23588,7 +23591,7 @@
     </row>
     <row r="873" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B873" s="3" t="s">
         <v>31</v>
@@ -23611,7 +23614,7 @@
     </row>
     <row r="874" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B874" s="3" t="s">
         <v>31</v>
@@ -23634,7 +23637,7 @@
     </row>
     <row r="875" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B875" s="3" t="s">
         <v>31</v>
@@ -23657,7 +23660,7 @@
     </row>
     <row r="876" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B876" s="3" t="s">
         <v>31</v>
@@ -23680,7 +23683,7 @@
     </row>
     <row r="877" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B877" s="3" t="s">
         <v>31</v>
@@ -23703,7 +23706,7 @@
     </row>
     <row r="878" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B878" s="3" t="s">
         <v>31</v>
@@ -23726,7 +23729,7 @@
     </row>
     <row r="879" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B879" s="3" t="s">
         <v>31</v>
@@ -23749,7 +23752,7 @@
     </row>
     <row r="880" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B880" s="3" t="s">
         <v>31</v>
@@ -23772,7 +23775,7 @@
     </row>
     <row r="881" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B881" s="3" t="s">
         <v>31</v>
@@ -23795,7 +23798,7 @@
     </row>
     <row r="882" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B882" s="3" t="s">
         <v>31</v>
@@ -23818,7 +23821,7 @@
     </row>
     <row r="883" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B883" s="3" t="s">
         <v>31</v>
@@ -23841,7 +23844,7 @@
     </row>
     <row r="884" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A884" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B884" s="3" t="s">
         <v>31</v>
@@ -23864,7 +23867,7 @@
     </row>
     <row r="885" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B885" s="3" t="s">
         <v>31</v>
@@ -23887,7 +23890,7 @@
     </row>
     <row r="886" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A886" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B886" s="3" t="s">
         <v>31</v>
@@ -23910,7 +23913,7 @@
     </row>
     <row r="887" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B887" s="3" t="s">
         <v>31</v>
@@ -23933,7 +23936,7 @@
     </row>
     <row r="888" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A888" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B888" s="3" t="s">
         <v>31</v>
@@ -23956,7 +23959,7 @@
     </row>
     <row r="889" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A889" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B889" s="3" t="s">
         <v>31</v>
@@ -23979,7 +23982,7 @@
     </row>
     <row r="890" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A890" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B890" s="3" t="s">
         <v>31</v>
@@ -24002,7 +24005,7 @@
     </row>
     <row r="891" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A891" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B891" s="3" t="s">
         <v>31</v>
@@ -24025,7 +24028,7 @@
     </row>
     <row r="892" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A892" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B892" s="3" t="s">
         <v>31</v>
@@ -24048,7 +24051,7 @@
     </row>
     <row r="893" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A893" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B893" s="3" t="s">
         <v>31</v>
@@ -24071,7 +24074,7 @@
     </row>
     <row r="894" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A894" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B894" s="3" t="s">
         <v>31</v>
@@ -24094,7 +24097,7 @@
     </row>
     <row r="895" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A895" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B895" s="3" t="s">
         <v>31</v>
@@ -24117,7 +24120,7 @@
     </row>
     <row r="896" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A896" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B896" s="3" t="s">
         <v>31</v>
@@ -24140,7 +24143,7 @@
     </row>
     <row r="897" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B897" s="3" t="s">
         <v>31</v>
@@ -24163,7 +24166,7 @@
     </row>
     <row r="898" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B898" s="3" t="s">
         <v>32</v>
@@ -24186,7 +24189,7 @@
     </row>
     <row r="899" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B899" s="3" t="s">
         <v>32</v>
@@ -24209,7 +24212,7 @@
     </row>
     <row r="900" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B900" s="3" t="s">
         <v>32</v>
@@ -24232,7 +24235,7 @@
     </row>
     <row r="901" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B901" s="3" t="s">
         <v>32</v>
@@ -24255,7 +24258,7 @@
     </row>
     <row r="902" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B902" s="3" t="s">
         <v>32</v>
@@ -24278,7 +24281,7 @@
     </row>
     <row r="903" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B903" s="3" t="s">
         <v>32</v>
@@ -24301,7 +24304,7 @@
     </row>
     <row r="904" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B904" s="3" t="s">
         <v>32</v>
@@ -24324,7 +24327,7 @@
     </row>
     <row r="905" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A905" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B905" s="3" t="s">
         <v>32</v>
@@ -24347,7 +24350,7 @@
     </row>
     <row r="906" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B906" s="3" t="s">
         <v>32</v>
@@ -24370,7 +24373,7 @@
     </row>
     <row r="907" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A907" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B907" s="3" t="s">
         <v>32</v>
@@ -24393,7 +24396,7 @@
     </row>
     <row r="908" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A908" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B908" s="3" t="s">
         <v>32</v>
@@ -24416,7 +24419,7 @@
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A909" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B909" s="3" t="s">
         <v>32</v>
@@ -24439,7 +24442,7 @@
     </row>
     <row r="910" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A910" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B910" s="3" t="s">
         <v>32</v>
@@ -24462,7 +24465,7 @@
     </row>
     <row r="911" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A911" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B911" s="3" t="s">
         <v>32</v>
@@ -24485,7 +24488,7 @@
     </row>
     <row r="912" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A912" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B912" s="3" t="s">
         <v>32</v>
@@ -24508,7 +24511,7 @@
     </row>
     <row r="913" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A913" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B913" s="3" t="s">
         <v>32</v>
@@ -24531,7 +24534,7 @@
     </row>
     <row r="914" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A914" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B914" s="3" t="s">
         <v>32</v>
@@ -24554,7 +24557,7 @@
     </row>
     <row r="915" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A915" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B915" s="3" t="s">
         <v>32</v>
@@ -24577,7 +24580,7 @@
     </row>
     <row r="916" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A916" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B916" s="3" t="s">
         <v>32</v>
@@ -24600,7 +24603,7 @@
     </row>
     <row r="917" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A917" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B917" s="3" t="s">
         <v>32</v>
@@ -24623,7 +24626,7 @@
     </row>
     <row r="918" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A918" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B918" s="3" t="s">
         <v>32</v>
@@ -24646,7 +24649,7 @@
     </row>
     <row r="919" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A919" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B919" s="3" t="s">
         <v>32</v>
@@ -24669,7 +24672,7 @@
     </row>
     <row r="920" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A920" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B920" s="3" t="s">
         <v>32</v>
@@ -24692,7 +24695,7 @@
     </row>
     <row r="921" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A921" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B921" s="3" t="s">
         <v>32</v>
@@ -24715,7 +24718,7 @@
     </row>
     <row r="922" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A922" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B922" s="3" t="s">
         <v>32</v>
@@ -24738,7 +24741,7 @@
     </row>
     <row r="923" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A923" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B923" s="3" t="s">
         <v>32</v>
@@ -24761,7 +24764,7 @@
     </row>
     <row r="924" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A924" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B924" s="3" t="s">
         <v>32</v>
@@ -24784,7 +24787,7 @@
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A925" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B925" s="3" t="s">
         <v>32</v>
@@ -24807,7 +24810,7 @@
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A926" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B926" s="3" t="s">
         <v>32</v>
@@ -24830,7 +24833,7 @@
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B927" s="3" t="s">
         <v>32</v>
@@ -24853,7 +24856,7 @@
     </row>
     <row r="928" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A928" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B928" s="3" t="s">
         <v>32</v>
@@ -24876,7 +24879,7 @@
     </row>
     <row r="929" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A929" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B929" s="3" t="s">
         <v>32</v>
@@ -24899,7 +24902,7 @@
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A930" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B930" s="3" t="s">
         <v>33</v>
@@ -24922,7 +24925,7 @@
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A931" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B931" s="3" t="s">
         <v>33</v>
@@ -24945,7 +24948,7 @@
     </row>
     <row r="932" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A932" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B932" s="3" t="s">
         <v>33</v>
@@ -24968,7 +24971,7 @@
     </row>
     <row r="933" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A933" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B933" s="3" t="s">
         <v>33</v>
@@ -24991,7 +24994,7 @@
     </row>
     <row r="934" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A934" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B934" s="3" t="s">
         <v>33</v>
@@ -25014,7 +25017,7 @@
     </row>
     <row r="935" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A935" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B935" s="3" t="s">
         <v>33</v>
@@ -25037,7 +25040,7 @@
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A936" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B936" s="3" t="s">
         <v>33</v>
@@ -25060,7 +25063,7 @@
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A937" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B937" s="3" t="s">
         <v>33</v>
@@ -25083,7 +25086,7 @@
     </row>
     <row r="938" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A938" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B938" s="3" t="s">
         <v>33</v>
@@ -25106,7 +25109,7 @@
     </row>
     <row r="939" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A939" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B939" s="3" t="s">
         <v>33</v>
@@ -25129,7 +25132,7 @@
     </row>
     <row r="940" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A940" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B940" s="3" t="s">
         <v>33</v>
@@ -25152,7 +25155,7 @@
     </row>
     <row r="941" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A941" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B941" s="3" t="s">
         <v>33</v>
@@ -25175,7 +25178,7 @@
     </row>
     <row r="942" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A942" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B942" s="3" t="s">
         <v>33</v>
@@ -25198,7 +25201,7 @@
     </row>
     <row r="943" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A943" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B943" s="3" t="s">
         <v>33</v>
@@ -25221,7 +25224,7 @@
     </row>
     <row r="944" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A944" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B944" s="3" t="s">
         <v>33</v>
@@ -25244,7 +25247,7 @@
     </row>
     <row r="945" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A945" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B945" s="3" t="s">
         <v>33</v>
@@ -25267,7 +25270,7 @@
     </row>
     <row r="946" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A946" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B946" s="3" t="s">
         <v>33</v>
@@ -25290,7 +25293,7 @@
     </row>
     <row r="947" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A947" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B947" s="3" t="s">
         <v>33</v>
@@ -25313,7 +25316,7 @@
     </row>
     <row r="948" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A948" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B948" s="3" t="s">
         <v>33</v>
@@ -25336,7 +25339,7 @@
     </row>
     <row r="949" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A949" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B949" s="3" t="s">
         <v>33</v>
@@ -25359,7 +25362,7 @@
     </row>
     <row r="950" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B950" s="3" t="s">
         <v>33</v>
@@ -25382,7 +25385,7 @@
     </row>
     <row r="951" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A951" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B951" s="3" t="s">
         <v>33</v>
@@ -25405,7 +25408,7 @@
     </row>
     <row r="952" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A952" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B952" s="3" t="s">
         <v>33</v>
@@ -25428,7 +25431,7 @@
     </row>
     <row r="953" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A953" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B953" s="3" t="s">
         <v>33</v>
@@ -25451,7 +25454,7 @@
     </row>
     <row r="954" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A954" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B954" s="3" t="s">
         <v>33</v>
@@ -25474,7 +25477,7 @@
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A955" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B955" s="3" t="s">
         <v>33</v>
@@ -25497,7 +25500,7 @@
     </row>
     <row r="956" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A956" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B956" s="3" t="s">
         <v>33</v>
@@ -25520,7 +25523,7 @@
     </row>
     <row r="957" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B957" s="3" t="s">
         <v>33</v>
@@ -25543,7 +25546,7 @@
     </row>
     <row r="958" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B958" s="3" t="s">
         <v>33</v>
@@ -25566,7 +25569,7 @@
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B959" s="3" t="s">
         <v>33</v>
@@ -25589,7 +25592,7 @@
     </row>
     <row r="960" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B960" s="3" t="s">
         <v>33</v>
@@ -25612,7 +25615,7 @@
     </row>
     <row r="961" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B961" s="3" t="s">
         <v>33</v>
@@ -25635,7 +25638,7 @@
     </row>
     <row r="962" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B962" s="3" t="s">
         <v>34</v>
@@ -25658,7 +25661,7 @@
     </row>
     <row r="963" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B963" s="3" t="s">
         <v>34</v>
@@ -25681,7 +25684,7 @@
     </row>
     <row r="964" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B964" s="3" t="s">
         <v>34</v>
@@ -25704,7 +25707,7 @@
     </row>
     <row r="965" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B965" s="3" t="s">
         <v>34</v>
@@ -25727,7 +25730,7 @@
     </row>
     <row r="966" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B966" s="3" t="s">
         <v>34</v>
@@ -25750,7 +25753,7 @@
     </row>
     <row r="967" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B967" s="3" t="s">
         <v>34</v>
@@ -25773,7 +25776,7 @@
     </row>
     <row r="968" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B968" s="3" t="s">
         <v>34</v>
@@ -25796,7 +25799,7 @@
     </row>
     <row r="969" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B969" s="3" t="s">
         <v>34</v>
@@ -25819,7 +25822,7 @@
     </row>
     <row r="970" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B970" s="3" t="s">
         <v>34</v>
@@ -25842,7 +25845,7 @@
     </row>
     <row r="971" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B971" s="3" t="s">
         <v>34</v>
@@ -25865,7 +25868,7 @@
     </row>
     <row r="972" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B972" s="3" t="s">
         <v>34</v>
@@ -25888,7 +25891,7 @@
     </row>
     <row r="973" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B973" s="3" t="s">
         <v>34</v>
@@ -25911,7 +25914,7 @@
     </row>
     <row r="974" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B974" s="3" t="s">
         <v>34</v>
@@ -25934,7 +25937,7 @@
     </row>
     <row r="975" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B975" s="3" t="s">
         <v>34</v>
@@ -25957,7 +25960,7 @@
     </row>
     <row r="976" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B976" s="3" t="s">
         <v>34</v>
@@ -25980,7 +25983,7 @@
     </row>
     <row r="977" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B977" s="3" t="s">
         <v>34</v>
@@ -26003,7 +26006,7 @@
     </row>
     <row r="978" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B978" s="3" t="s">
         <v>34</v>
@@ -26026,7 +26029,7 @@
     </row>
     <row r="979" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B979" s="3" t="s">
         <v>34</v>
@@ -26049,7 +26052,7 @@
     </row>
     <row r="980" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B980" s="3" t="s">
         <v>34</v>
@@ -26072,7 +26075,7 @@
     </row>
     <row r="981" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B981" s="3" t="s">
         <v>34</v>
@@ -26095,7 +26098,7 @@
     </row>
     <row r="982" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B982" s="3" t="s">
         <v>34</v>
@@ -26118,7 +26121,7 @@
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B983" s="3" t="s">
         <v>34</v>
@@ -26141,7 +26144,7 @@
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B984" s="3" t="s">
         <v>34</v>
@@ -26164,7 +26167,7 @@
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B985" s="3" t="s">
         <v>34</v>
@@ -26187,7 +26190,7 @@
     </row>
     <row r="986" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B986" s="3" t="s">
         <v>34</v>
@@ -26210,7 +26213,7 @@
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B987" s="3" t="s">
         <v>34</v>
@@ -26233,7 +26236,7 @@
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B988" s="3" t="s">
         <v>34</v>
@@ -26256,7 +26259,7 @@
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B989" s="3" t="s">
         <v>34</v>
@@ -26279,7 +26282,7 @@
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B990" s="3" t="s">
         <v>34</v>
@@ -26302,7 +26305,7 @@
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B991" s="3" t="s">
         <v>34</v>
@@ -26325,7 +26328,7 @@
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B992" s="3" t="s">
         <v>34</v>
@@ -26348,7 +26351,7 @@
     </row>
     <row r="993" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A993" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B993" s="3" t="s">
         <v>34</v>
@@ -26371,7 +26374,7 @@
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A994" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B994" s="3" t="s">
         <v>35</v>
@@ -26394,7 +26397,7 @@
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A995" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B995" s="3" t="s">
         <v>35</v>
@@ -26417,7 +26420,7 @@
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A996" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B996" s="3" t="s">
         <v>35</v>
@@ -26440,7 +26443,7 @@
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A997" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B997" s="3" t="s">
         <v>35</v>
@@ -26463,7 +26466,7 @@
     </row>
     <row r="998" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A998" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B998" s="3" t="s">
         <v>35</v>
@@ -26486,7 +26489,7 @@
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A999" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B999" s="3" t="s">
         <v>35</v>
@@ -26509,7 +26512,7 @@
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1000" s="1" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B1000" s="3" t="s">
         <v>35</v>
@@ -26524,9 +26527,32 @@
         <v>3000</v>
       </c>
       <c r="F1000" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G1000" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1001" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B1001" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1001" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E1001" s="2">
+        <v>280</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1001" t="s">
         <v>41</v>
       </c>
     </row>
